--- a/salidas/empresas/TMUS.xlsx
+++ b/salidas/empresas/TMUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B5" t="n">
-        <v>57.69760513305664</v>
+        <v>57.69759750366211</v>
       </c>
       <c r="C5" t="n">
         <v>73.23999786376953</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B7" t="n">
-        <v>42.98171615600586</v>
+        <v>42.98172378540039</v>
       </c>
       <c r="C7" t="n">
         <v>54.56000137329102</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B8" t="n">
-        <v>35.45046615600586</v>
+        <v>35.45045852661133</v>
       </c>
       <c r="C8" t="n">
         <v>45</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B9" t="n">
-        <v>26.94235229492188</v>
+        <v>26.94235610961914</v>
       </c>
       <c r="C9" t="n">
         <v>34.20000076293945</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B11" t="n">
-        <v>28.64397811889648</v>
+        <v>28.64397430419922</v>
       </c>
       <c r="C11" t="n">
         <v>36.36000061035156</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B12" t="n">
-        <v>25.13044166564941</v>
+        <v>25.13043785095215</v>
       </c>
       <c r="C12" t="n">
         <v>31.89999961853027</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B14" t="n">
-        <v>30.9443187713623</v>
+        <v>30.94431304931641</v>
       </c>
       <c r="C14" t="n">
         <v>39.27999877929688</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B16" t="n">
-        <v>27.90345001220703</v>
+        <v>27.90345191955566</v>
       </c>
       <c r="C16" t="n">
         <v>35.41999816894531</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B17" t="n">
-        <v>26.20183372497559</v>
+        <v>26.20182991027832</v>
       </c>
       <c r="C17" t="n">
         <v>33.2599983215332</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B21" t="n">
-        <v>23.06643486022949</v>
+        <v>23.06643295288086</v>
       </c>
       <c r="C21" t="n">
         <v>29.28000068664551</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B23" t="n">
-        <v>21.41207885742188</v>
+        <v>21.41208076477051</v>
       </c>
       <c r="C23" t="n">
         <v>27.18000030517578</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B24" t="n">
-        <v>22.84585571289062</v>
+        <v>22.84585189819336</v>
       </c>
       <c r="C24" t="n">
         <v>29</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B25" t="n">
-        <v>26.91083908081055</v>
+        <v>26.91084289550781</v>
       </c>
       <c r="C25" t="n">
         <v>34.15999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B26" t="n">
-        <v>26.92659950256348</v>
+        <v>26.92659759521484</v>
       </c>
       <c r="C26" t="n">
         <v>34.18000030517578</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B27" t="n">
-        <v>26.98961639404297</v>
+        <v>26.9896183013916</v>
       </c>
       <c r="C27" t="n">
         <v>34.2599983215332</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B28" t="n">
-        <v>20.97091674804688</v>
+        <v>20.97092056274414</v>
       </c>
       <c r="C28" t="n">
         <v>26.6200008392334</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B29" t="n">
-        <v>18.67057800292969</v>
+        <v>18.67058181762695</v>
       </c>
       <c r="C29" t="n">
         <v>23.70000076293945</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B31" t="n">
-        <v>14.74739170074463</v>
+        <v>14.74739456176758</v>
       </c>
       <c r="C31" t="n">
         <v>18.71999931335449</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B32" t="n">
-        <v>9.815839767456055</v>
+        <v>9.815840721130371</v>
       </c>
       <c r="C32" t="n">
         <v>12.46000003814697</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B33" t="n">
-        <v>9.926131248474121</v>
+        <v>9.926130294799805</v>
       </c>
       <c r="C33" t="n">
         <v>12.60000038146973</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B34" t="n">
-        <v>12.02164649963379</v>
+        <v>12.02164554595947</v>
       </c>
       <c r="C34" t="n">
         <v>15.26000022888184</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B35" t="n">
-        <v>8.87049388885498</v>
+        <v>8.870494842529297</v>
       </c>
       <c r="C35" t="n">
         <v>11.26000022888184</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B38" t="n">
-        <v>12.02164649963379</v>
+        <v>12.02164554595947</v>
       </c>
       <c r="C38" t="n">
         <v>15.26000022888184</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B39" t="n">
-        <v>14.1644287109375</v>
+        <v>14.16443061828613</v>
       </c>
       <c r="C39" t="n">
         <v>17.97999954223633</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B41" t="n">
-        <v>14.10140800476074</v>
+        <v>14.10140705108643</v>
       </c>
       <c r="C41" t="n">
         <v>17.89999961853027</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B42" t="n">
-        <v>14.08565044403076</v>
+        <v>14.08564949035645</v>
       </c>
       <c r="C42" t="n">
         <v>17.8799991607666</v>
@@ -1267,11 +1279,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B43" t="n">
-        <v>16.48052978515625</v>
+        <v>16.48052787780762</v>
       </c>
       <c r="C43" t="n">
         <v>20.92000007629395</v>
@@ -1292,11 +1304,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B44" t="n">
-        <v>16.3859920501709</v>
+        <v>16.38599014282227</v>
       </c>
       <c r="C44" t="n">
         <v>20.79999923706055</v>
@@ -1317,11 +1329,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B45" t="n">
-        <v>19.14324951171875</v>
+        <v>19.14325141906738</v>
       </c>
       <c r="C45" t="n">
         <v>24.29999923706055</v>
@@ -1342,7 +1354,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B46" t="n">
@@ -1367,11 +1379,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B47" t="n">
-        <v>20.3722038269043</v>
+        <v>20.37220573425293</v>
       </c>
       <c r="C47" t="n">
         <v>25.86000061035156</v>
@@ -1392,11 +1404,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B48" t="n">
-        <v>22.68829917907715</v>
+        <v>22.68829154968262</v>
       </c>
       <c r="C48" t="n">
         <v>28.79999923706055</v>
@@ -1417,11 +1429,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B49" t="n">
-        <v>25.58735656738281</v>
+        <v>25.58735466003418</v>
       </c>
       <c r="C49" t="n">
         <v>32.47999954223633</v>
@@ -1442,11 +1454,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B50" t="n">
-        <v>26.51694488525391</v>
+        <v>26.51694679260254</v>
       </c>
       <c r="C50" t="n">
         <v>33.65999984741211</v>
@@ -1467,11 +1479,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B51" t="n">
-        <v>28.20281600952148</v>
+        <v>28.20281410217285</v>
       </c>
       <c r="C51" t="n">
         <v>35.79999923706055</v>
@@ -1492,7 +1504,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B52" t="n">
@@ -1517,11 +1529,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B53" t="n">
-        <v>25.65038299560547</v>
+        <v>25.65038108825684</v>
       </c>
       <c r="C53" t="n">
         <v>32.56000137329102</v>
@@ -1542,11 +1554,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B54" t="n">
-        <v>17.58343315124512</v>
+        <v>17.58342933654785</v>
       </c>
       <c r="C54" t="n">
         <v>22.31999969482422</v>
@@ -1567,11 +1579,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B55" t="n">
-        <v>13.72326755523682</v>
+        <v>13.72326946258545</v>
       </c>
       <c r="C55" t="n">
         <v>17.42000007629395</v>
@@ -1592,7 +1604,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B56" t="n">
@@ -1617,11 +1629,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B57" t="n">
-        <v>13.20332813262939</v>
+        <v>13.20332908630371</v>
       </c>
       <c r="C57" t="n">
         <v>16.76000022888184</v>
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B58" t="n">
@@ -1667,7 +1679,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B59" t="n">
@@ -1692,7 +1704,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B60" t="n">
@@ -1721,11 +1733,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B61" t="n">
-        <v>14.21169662475586</v>
+        <v>14.21169757843018</v>
       </c>
       <c r="C61" t="n">
         <v>18.04000091552734</v>
@@ -1750,11 +1762,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B62" t="n">
-        <v>11.50170707702637</v>
+        <v>11.50170803070068</v>
       </c>
       <c r="C62" t="n">
         <v>14.60000038146973</v>
@@ -1779,11 +1791,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B63" t="n">
-        <v>10.0836877822876</v>
+        <v>10.08368873596191</v>
       </c>
       <c r="C63" t="n">
         <v>12.80000019073486</v>
@@ -1808,11 +1820,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B64" t="n">
-        <v>9.532236099243164</v>
+        <v>9.532234191894531</v>
       </c>
       <c r="C64" t="n">
         <v>12.10000038146973</v>
@@ -1837,7 +1849,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B65" t="n">
@@ -1866,7 +1878,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B66" t="n">
@@ -1895,11 +1907,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B67" t="n">
-        <v>18.44999504089355</v>
+        <v>18.44999694824219</v>
       </c>
       <c r="C67" t="n">
         <v>23.42000007629395</v>
@@ -1924,11 +1936,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B68" t="n">
-        <v>16.08662986755371</v>
+        <v>16.08663177490234</v>
       </c>
       <c r="C68" t="n">
         <v>20.42000007629395</v>
@@ -1953,7 +1965,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B69" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B70" t="n">
@@ -2011,11 +2023,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B71" t="n">
-        <v>15.80303001403809</v>
+        <v>15.80302619934082</v>
       </c>
       <c r="C71" t="n">
         <v>20.05999946594238</v>
@@ -2040,11 +2052,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B72" t="n">
-        <v>15.44064521789551</v>
+        <v>15.44064712524414</v>
       </c>
       <c r="C72" t="n">
         <v>19.60000038146973</v>
@@ -2069,11 +2081,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B73" t="n">
-        <v>17.17377853393555</v>
+        <v>17.17377662658691</v>
       </c>
       <c r="C73" t="n">
         <v>21.79999923706055</v>
@@ -2098,11 +2110,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B74" t="n">
-        <v>18.65481948852539</v>
+        <v>18.65482139587402</v>
       </c>
       <c r="C74" t="n">
         <v>23.68000030517578</v>
@@ -2127,7 +2139,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B75" t="n">
@@ -2156,11 +2168,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B76" t="n">
-        <v>23.58950614929199</v>
+        <v>23.58950996398926</v>
       </c>
       <c r="C76" t="n">
         <v>24.80999946594238</v>
@@ -2185,11 +2197,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B77" t="n">
-        <v>22.92394256591797</v>
+        <v>22.9239444732666</v>
       </c>
       <c r="C77" t="n">
         <v>24.11000061035156</v>
@@ -2214,7 +2226,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B78" t="n">
@@ -2243,11 +2255,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B79" t="n">
-        <v>24.69244003295898</v>
+        <v>24.69244194030762</v>
       </c>
       <c r="C79" t="n">
         <v>25.96999931335449</v>
@@ -2272,11 +2284,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B80" t="n">
-        <v>26.36586380004883</v>
+        <v>26.3658618927002</v>
       </c>
       <c r="C80" t="n">
         <v>27.72999954223633</v>
@@ -2301,11 +2313,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B81" t="n">
-        <v>24.7304744720459</v>
+        <v>24.73047256469727</v>
       </c>
       <c r="C81" t="n">
         <v>26.01000022888184</v>
@@ -2330,7 +2342,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B82" t="n">
@@ -2359,11 +2371,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B83" t="n">
-        <v>29.0661506652832</v>
+        <v>29.06615257263184</v>
       </c>
       <c r="C83" t="n">
         <v>30.56999969482422</v>
@@ -2388,7 +2400,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B84" t="n">
@@ -2415,11 +2427,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B85" t="n">
-        <v>31.4051399230957</v>
+        <v>31.40513610839844</v>
       </c>
       <c r="C85" t="n">
         <v>33.02999877929688</v>
@@ -2442,11 +2454,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B86" t="n">
-        <v>27.84912109375</v>
+        <v>27.84912490844727</v>
       </c>
       <c r="C86" t="n">
         <v>29.29000091552734</v>
@@ -2469,11 +2481,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B87" t="n">
-        <v>32.64118576049805</v>
+        <v>32.64117813110352</v>
       </c>
       <c r="C87" t="n">
         <v>34.33000183105469</v>
@@ -2496,11 +2508,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B88" t="n">
-        <v>31.96611022949219</v>
+        <v>31.96611213684082</v>
       </c>
       <c r="C88" t="n">
         <v>33.61999893188477</v>
@@ -2523,11 +2535,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B89" t="n">
-        <v>31.31955718994141</v>
+        <v>31.31956481933594</v>
       </c>
       <c r="C89" t="n">
         <v>32.93999862670898</v>
@@ -2552,11 +2564,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B90" t="n">
-        <v>28.60025787353516</v>
+        <v>28.60025596618652</v>
       </c>
       <c r="C90" t="n">
         <v>30.07999992370605</v>
@@ -2581,11 +2593,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B91" t="n">
-        <v>27.44978332519531</v>
+        <v>27.44978713989258</v>
       </c>
       <c r="C91" t="n">
         <v>28.8700008392334</v>
@@ -2610,11 +2622,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B92" t="n">
-        <v>27.75404357910156</v>
+        <v>27.75403785705566</v>
       </c>
       <c r="C92" t="n">
         <v>29.19000053405762</v>
@@ -2639,11 +2651,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B93" t="n">
-        <v>27.75404357910156</v>
+        <v>27.75403785705566</v>
       </c>
       <c r="C93" t="n">
         <v>29.19000053405762</v>
@@ -2668,11 +2680,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B94" t="n">
-        <v>25.6147289276123</v>
+        <v>25.61472511291504</v>
       </c>
       <c r="C94" t="n">
         <v>26.94000053405762</v>
@@ -2697,11 +2709,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B95" t="n">
-        <v>28.69533538818359</v>
+        <v>28.69533920288086</v>
       </c>
       <c r="C95" t="n">
         <v>30.18000030517578</v>
@@ -2726,11 +2738,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B96" t="n">
-        <v>31.4051399230957</v>
+        <v>31.40513610839844</v>
       </c>
       <c r="C96" t="n">
         <v>33.02999877929688</v>
@@ -2755,7 +2767,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B97" t="n">
@@ -2784,11 +2796,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B98" t="n">
-        <v>32.36545562744141</v>
+        <v>32.36545181274414</v>
       </c>
       <c r="C98" t="n">
         <v>34.04000091552734</v>
@@ -2813,11 +2825,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B99" t="n">
-        <v>36.96736145019531</v>
+        <v>36.96735382080078</v>
       </c>
       <c r="C99" t="n">
         <v>38.88000106811523</v>
@@ -2842,11 +2854,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B100" t="n">
-        <v>36.86276245117188</v>
+        <v>36.86276626586914</v>
       </c>
       <c r="C100" t="n">
         <v>38.77000045776367</v>
@@ -2871,11 +2883,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B101" t="n">
-        <v>38.65978622436523</v>
+        <v>38.65979385375977</v>
       </c>
       <c r="C101" t="n">
         <v>40.65999984741211</v>
@@ -2900,11 +2912,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B102" t="n">
-        <v>37.66145324707031</v>
+        <v>37.66143417358398</v>
       </c>
       <c r="C102" t="n">
         <v>39.61000061035156</v>
@@ -2929,11 +2941,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B103" t="n">
-        <v>37.85160827636719</v>
+        <v>37.85160064697266</v>
       </c>
       <c r="C103" t="n">
         <v>39.81000137329102</v>
@@ -2958,7 +2970,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B104" t="n">
@@ -2987,11 +2999,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B105" t="n">
-        <v>33.75363159179688</v>
+        <v>33.75362396240234</v>
       </c>
       <c r="C105" t="n">
         <v>35.5</v>
@@ -3016,11 +3028,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B106" t="n">
-        <v>37.1955451965332</v>
+        <v>37.19555282592773</v>
       </c>
       <c r="C106" t="n">
         <v>39.11999893188477</v>
@@ -3045,7 +3057,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B107" t="n">
@@ -3074,7 +3086,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B108" t="n">
@@ -3103,11 +3115,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B109" t="n">
-        <v>36.41588592529297</v>
+        <v>36.4158821105957</v>
       </c>
       <c r="C109" t="n">
         <v>38.29999923706055</v>
@@ -3132,11 +3144,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B110" t="n">
-        <v>37.34767532348633</v>
+        <v>37.34767150878906</v>
       </c>
       <c r="C110" t="n">
         <v>39.27999877929688</v>
@@ -3161,11 +3173,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B111" t="n">
-        <v>40.65647888183594</v>
+        <v>40.65648651123047</v>
       </c>
       <c r="C111" t="n">
         <v>42.7599983215332</v>
@@ -3190,7 +3202,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B112" t="n">
@@ -3219,11 +3231,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B113" t="n">
-        <v>44.06036758422852</v>
+        <v>44.06037139892578</v>
       </c>
       <c r="C113" t="n">
         <v>46.34000015258789</v>
@@ -3248,11 +3260,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B114" t="n">
-        <v>44.06036758422852</v>
+        <v>44.06037139892578</v>
       </c>
       <c r="C114" t="n">
         <v>46.34000015258789</v>
@@ -3277,11 +3289,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B115" t="n">
-        <v>44.42168045043945</v>
+        <v>44.42167282104492</v>
       </c>
       <c r="C115" t="n">
         <v>46.72000122070312</v>
@@ -3306,7 +3318,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B116" t="n">
@@ -3335,11 +3347,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B117" t="n">
-        <v>51.54321670532227</v>
+        <v>51.54320526123047</v>
       </c>
       <c r="C117" t="n">
         <v>54.20999908447266</v>
@@ -3364,7 +3376,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B118" t="n">
@@ -3393,11 +3405,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B119" t="n">
-        <v>59.20671844482422</v>
+        <v>59.20671463012695</v>
       </c>
       <c r="C119" t="n">
         <v>62.27000045776367</v>
@@ -3422,11 +3434,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B120" t="n">
-        <v>59.45392990112305</v>
+        <v>59.45393371582031</v>
       </c>
       <c r="C120" t="n">
         <v>62.52999877929688</v>
@@ -3451,11 +3463,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B121" t="n">
-        <v>61.41257476806641</v>
+        <v>61.41258239746094</v>
       </c>
       <c r="C121" t="n">
         <v>64.58999633789062</v>
@@ -3480,11 +3492,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B122" t="n">
-        <v>63.96074676513672</v>
+        <v>63.96073532104492</v>
       </c>
       <c r="C122" t="n">
         <v>67.26999664306641</v>
@@ -3509,11 +3521,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B123" t="n">
-        <v>64.10336303710938</v>
+        <v>64.10337066650391</v>
       </c>
       <c r="C123" t="n">
         <v>67.41999816894531</v>
@@ -3538,7 +3550,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B124" t="n">
@@ -3567,11 +3579,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B125" t="n">
-        <v>58.62671661376953</v>
+        <v>58.62672424316406</v>
       </c>
       <c r="C125" t="n">
         <v>61.65999984741211</v>
@@ -3596,11 +3608,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B126" t="n">
-        <v>61.52667999267578</v>
+        <v>61.52668380737305</v>
       </c>
       <c r="C126" t="n">
         <v>64.70999908447266</v>
@@ -3625,11 +3637,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B127" t="n">
-        <v>58.62671661376953</v>
+        <v>58.62672424316406</v>
       </c>
       <c r="C127" t="n">
         <v>61.65999984741211</v>
@@ -3654,11 +3666,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B128" t="n">
-        <v>56.8297004699707</v>
+        <v>56.82970428466797</v>
       </c>
       <c r="C128" t="n">
         <v>59.77000045776367</v>
@@ -3683,7 +3695,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B129" t="n">
@@ -3712,11 +3724,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B130" t="n">
-        <v>60.38571548461914</v>
+        <v>60.38571929931641</v>
       </c>
       <c r="C130" t="n">
         <v>63.5099983215332</v>
@@ -3741,11 +3753,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B131" t="n">
-        <v>61.89749526977539</v>
+        <v>61.89749908447266</v>
       </c>
       <c r="C131" t="n">
         <v>65.09999847412109</v>
@@ -3770,11 +3782,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B132" t="n">
-        <v>57.62836837768555</v>
+        <v>57.62837600708008</v>
       </c>
       <c r="C132" t="n">
         <v>60.61000061035156</v>
@@ -3799,7 +3811,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B133" t="n">
@@ -3828,11 +3840,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B134" t="n">
-        <v>57.53329849243164</v>
+        <v>57.53329467773438</v>
       </c>
       <c r="C134" t="n">
         <v>60.5099983215332</v>
@@ -3857,7 +3869,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B135" t="n">
@@ -3886,7 +3898,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B136" t="n">
@@ -3915,7 +3927,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B137" t="n">
@@ -3944,11 +3956,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B138" t="n">
-        <v>62.79124450683594</v>
+        <v>62.79125595092773</v>
       </c>
       <c r="C138" t="n">
         <v>66.04000091552734</v>
@@ -3973,11 +3985,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B139" t="n">
-        <v>66.72760009765625</v>
+        <v>66.72759246826172</v>
       </c>
       <c r="C139" t="n">
         <v>70.18000030517578</v>
@@ -4002,11 +4014,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B140" t="n">
-        <v>65.17777252197266</v>
+        <v>65.17778015136719</v>
       </c>
       <c r="C140" t="n">
         <v>68.55000305175781</v>
@@ -4031,11 +4043,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B141" t="n">
-        <v>65.08271026611328</v>
+        <v>65.08270263671875</v>
       </c>
       <c r="C141" t="n">
         <v>68.44999694824219</v>
@@ -4060,7 +4072,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B142" t="n">
@@ -4089,11 +4101,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B143" t="n">
-        <v>66.19513702392578</v>
+        <v>66.19514465332031</v>
       </c>
       <c r="C143" t="n">
         <v>69.62000274658203</v>
@@ -4118,11 +4130,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B144" t="n">
-        <v>68.65773773193359</v>
+        <v>68.65773010253906</v>
       </c>
       <c r="C144" t="n">
         <v>72.20999908447266</v>
@@ -4147,7 +4159,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B145" t="n">
@@ -4176,7 +4188,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B146" t="n">
@@ -4205,7 +4217,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B147" t="n">
@@ -4234,11 +4246,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B148" t="n">
-        <v>70.4927978515625</v>
+        <v>70.49278259277344</v>
       </c>
       <c r="C148" t="n">
         <v>74.13999938964844</v>
@@ -4263,11 +4275,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B149" t="n">
-        <v>75.80778503417969</v>
+        <v>75.80779266357422</v>
       </c>
       <c r="C149" t="n">
         <v>79.73000335693359</v>
@@ -4292,11 +4304,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B150" t="n">
-        <v>74.21043395996094</v>
+        <v>74.21044158935547</v>
       </c>
       <c r="C150" t="n">
         <v>78.05000305175781</v>
@@ -4321,7 +4333,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B151" t="n">
@@ -4350,11 +4362,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B152" t="n">
-        <v>78.59365844726562</v>
+        <v>78.59366607666016</v>
       </c>
       <c r="C152" t="n">
         <v>82.66000366210938</v>
@@ -4379,7 +4391,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B153" t="n">
@@ -4408,11 +4420,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B154" t="n">
-        <v>74.56223297119141</v>
+        <v>74.56224822998047</v>
       </c>
       <c r="C154" t="n">
         <v>78.41999816894531</v>
@@ -4437,11 +4449,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B155" t="n">
-        <v>75.29438018798828</v>
+        <v>75.29437255859375</v>
       </c>
       <c r="C155" t="n">
         <v>79.19000244140625</v>
@@ -4466,7 +4478,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B156" t="n">
@@ -4495,11 +4507,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B157" t="n">
-        <v>79.77265167236328</v>
+        <v>79.77265930175781</v>
       </c>
       <c r="C157" t="n">
         <v>83.90000152587891</v>
@@ -4524,7 +4536,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B158" t="n">
@@ -4553,11 +4565,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B159" t="n">
-        <v>95.11867523193359</v>
+        <v>95.11866760253906</v>
       </c>
       <c r="C159" t="n">
         <v>100.0400009155273</v>
@@ -4582,11 +4594,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>99.0264892578125</v>
+        <v>99.02648162841797</v>
       </c>
       <c r="C160" t="n">
         <v>104.1500015258789</v>
@@ -4611,7 +4623,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B161" t="n">
@@ -4640,11 +4652,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B162" t="n">
-        <v>110.9400939941406</v>
+        <v>110.9400863647461</v>
       </c>
       <c r="C162" t="n">
         <v>116.6800003051758</v>
@@ -4669,11 +4681,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B163" t="n">
-        <v>108.7342224121094</v>
+        <v>108.7342300415039</v>
       </c>
       <c r="C163" t="n">
         <v>114.3600006103516</v>
@@ -4698,7 +4710,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B164" t="n">
@@ -4727,11 +4739,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B165" t="n">
-        <v>126.4002151489258</v>
+        <v>126.4002075195312</v>
       </c>
       <c r="C165" t="n">
         <v>132.9400024414062</v>
@@ -4756,7 +4768,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B166" t="n">
@@ -4785,11 +4797,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B167" t="n">
-        <v>119.8776626586914</v>
+        <v>119.8776779174805</v>
       </c>
       <c r="C167" t="n">
         <v>126.0800018310547</v>
@@ -4814,11 +4826,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B168" t="n">
-        <v>114.0682373046875</v>
+        <v>114.068244934082</v>
       </c>
       <c r="C168" t="n">
         <v>119.9700012207031</v>
@@ -4843,11 +4855,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B169" t="n">
-        <v>119.1265335083008</v>
+        <v>119.1265411376953</v>
       </c>
       <c r="C169" t="n">
         <v>125.2900009155273</v>
@@ -4872,7 +4884,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B170" t="n">
@@ -4901,11 +4913,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>134.4915771484375</v>
+        <v>134.4915618896484</v>
       </c>
       <c r="C171" t="n">
         <v>141.4499969482422</v>
@@ -4930,11 +4942,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B172" t="n">
-        <v>137.705322265625</v>
+        <v>137.7052764892578</v>
       </c>
       <c r="C172" t="n">
         <v>144.8300018310547</v>
@@ -4959,7 +4971,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B173" t="n">
@@ -4988,7 +5000,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B174" t="n">
@@ -5017,11 +5029,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B175" t="n">
-        <v>121.4750213623047</v>
+        <v>121.4750442504883</v>
       </c>
       <c r="C175" t="n">
         <v>127.7600021362305</v>
@@ -5046,11 +5058,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B176" t="n">
-        <v>109.3712615966797</v>
+        <v>109.3712692260742</v>
       </c>
       <c r="C176" t="n">
         <v>115.0299987792969</v>
@@ -5075,7 +5087,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B177" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B178" t="n">
@@ -5133,11 +5145,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B179" t="n">
-        <v>102.8487243652344</v>
+        <v>102.8487167358398</v>
       </c>
       <c r="C179" t="n">
         <v>108.1699981689453</v>
@@ -5162,7 +5174,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B180" t="n">
@@ -5191,11 +5203,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B181" t="n">
-        <v>122.036018371582</v>
+        <v>122.0360107421875</v>
       </c>
       <c r="C181" t="n">
         <v>128.3500061035156</v>
@@ -5220,11 +5232,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B182" t="n">
-        <v>117.0822906494141</v>
+        <v>117.0823059082031</v>
       </c>
       <c r="C182" t="n">
         <v>123.1399993896484</v>
@@ -5249,11 +5261,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B183" t="n">
-        <v>126.7329864501953</v>
+        <v>126.7329635620117</v>
       </c>
       <c r="C183" t="n">
         <v>133.2899932861328</v>
@@ -5278,11 +5290,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B184" t="n">
-        <v>127.9214935302734</v>
+        <v>127.9214706420898</v>
       </c>
       <c r="C184" t="n">
         <v>134.5399932861328</v>
@@ -5307,11 +5319,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B185" t="n">
-        <v>136.0223541259766</v>
+        <v>136.0223693847656</v>
       </c>
       <c r="C185" t="n">
         <v>143.0599975585938</v>
@@ -5336,11 +5348,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B186" t="n">
-        <v>136.8780975341797</v>
+        <v>136.8780822753906</v>
       </c>
       <c r="C186" t="n">
         <v>143.9600067138672</v>
@@ -5365,11 +5377,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B187" t="n">
-        <v>127.5697021484375</v>
+        <v>127.569694519043</v>
       </c>
       <c r="C187" t="n">
         <v>134.1699981689453</v>
@@ -5394,7 +5406,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B188" t="n">
@@ -5423,11 +5435,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B189" t="n">
-        <v>144.0091247558594</v>
+        <v>144.0091400146484</v>
       </c>
       <c r="C189" t="n">
         <v>151.4600067138672</v>
@@ -5452,11 +5464,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B190" t="n">
-        <v>133.1128997802734</v>
+        <v>133.1128845214844</v>
       </c>
       <c r="C190" t="n">
         <v>140</v>
@@ -5481,7 +5493,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B191" t="n">
@@ -5510,11 +5522,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B192" t="n">
-        <v>135.1856536865234</v>
+        <v>135.1856384277344</v>
       </c>
       <c r="C192" t="n">
         <v>142.1799926757812</v>
@@ -5539,11 +5551,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B193" t="n">
-        <v>137.7147979736328</v>
+        <v>137.7147827148438</v>
       </c>
       <c r="C193" t="n">
         <v>144.8399963378906</v>
@@ -5568,11 +5580,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B194" t="n">
-        <v>136.8210601806641</v>
+        <v>136.821044921875</v>
       </c>
       <c r="C194" t="n">
         <v>143.8999938964844</v>
@@ -5597,7 +5609,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B195" t="n">
@@ -5626,11 +5638,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B196" t="n">
-        <v>132.0670013427734</v>
+        <v>132.0669860839844</v>
       </c>
       <c r="C196" t="n">
         <v>138.8999938964844</v>
@@ -5655,7 +5667,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B197" t="n">
@@ -5684,7 +5696,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B198" t="n">
@@ -5713,11 +5725,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B199" t="n">
-        <v>133.1604461669922</v>
+        <v>133.1604156494141</v>
       </c>
       <c r="C199" t="n">
         <v>140.0500030517578</v>
@@ -5742,11 +5754,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B200" t="n">
-        <v>136.7830047607422</v>
+        <v>136.7829895019531</v>
       </c>
       <c r="C200" t="n">
         <v>143.8600006103516</v>
@@ -5771,11 +5783,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B201" t="n">
-        <v>143.6732788085938</v>
+        <v>143.6732940673828</v>
       </c>
       <c r="C201" t="n">
         <v>150.4499969482422</v>
@@ -5800,7 +5812,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B202" t="n">
@@ -5829,7 +5841,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B203" t="n">
@@ -5858,7 +5870,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B204" t="n">
@@ -5887,11 +5899,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B205" t="n">
-        <v>156.4890899658203</v>
+        <v>156.4890594482422</v>
       </c>
       <c r="C205" t="n">
         <v>163.2200012207031</v>
@@ -5916,11 +5928,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B206" t="n">
-        <v>157.39990234375</v>
+        <v>157.3998870849609</v>
       </c>
       <c r="C206" t="n">
         <v>164.1699981689453</v>
@@ -5945,7 +5957,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B207" t="n">
@@ -5974,11 +5986,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B208" t="n">
-        <v>169.5602874755859</v>
+        <v>169.5602569580078</v>
       </c>
       <c r="C208" t="n">
         <v>176.1799926757812</v>
@@ -6003,11 +6015,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B209" t="n">
-        <v>175.4310760498047</v>
+        <v>175.4310607910156</v>
       </c>
       <c r="C209" t="n">
         <v>182.2799987792969</v>
@@ -6032,7 +6044,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B210" t="n">
@@ -6061,11 +6073,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B211" t="n">
-        <v>199.2536163330078</v>
+        <v>199.2536315917969</v>
       </c>
       <c r="C211" t="n">
         <v>206.3600006103516</v>
@@ -6090,7 +6102,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B212" t="n">
@@ -6119,11 +6131,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B213" t="n">
-        <v>239.2959747314453</v>
+        <v>239.2959899902344</v>
       </c>
       <c r="C213" t="n">
         <v>246.9400024414062</v>
@@ -6148,7 +6160,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B214" t="n">
@@ -6177,11 +6189,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B215" t="n">
-        <v>225.7584228515625</v>
+        <v>225.7584381103516</v>
       </c>
       <c r="C215" t="n">
         <v>232.9700012207031</v>
@@ -6206,11 +6218,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B216" t="n">
-        <v>262.2152099609375</v>
+        <v>262.2152404785156</v>
       </c>
       <c r="C216" t="n">
         <v>269.6900024414062</v>
@@ -6235,7 +6247,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B217" t="n">
@@ -6264,11 +6276,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B218" t="n">
-        <v>240.1055145263672</v>
+        <v>240.1054992675781</v>
       </c>
       <c r="C218" t="n">
         <v>246.9499969482422</v>
@@ -6293,11 +6305,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B219" t="n">
-        <v>236.3563232421875</v>
+        <v>236.3563385009766</v>
       </c>
       <c r="C219" t="n">
         <v>242.1999969482422</v>
@@ -6322,11 +6334,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B220" t="n">
-        <v>232.5113830566406</v>
+        <v>232.5113983154297</v>
       </c>
       <c r="C220" t="n">
         <v>238.2599945068359</v>
@@ -6351,7 +6363,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B221" t="n">
@@ -6380,7 +6392,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B222" t="n">
@@ -6409,7 +6421,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B223" t="n">
@@ -6438,11 +6450,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B224" t="n">
-        <v>205.7044982910156</v>
+        <v>205.7044830322266</v>
       </c>
       <c r="C224" t="n">
         <v>210.0500030517578</v>
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B225" t="n">
@@ -6496,7 +6508,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B226" t="n">
@@ -6525,7 +6537,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B227" t="n">
@@ -6554,7 +6566,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B228" t="n">
@@ -6583,7 +6595,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B229" t="n">
@@ -6612,7 +6624,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B230" t="n">
@@ -6641,7 +6653,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B231" t="n">
@@ -6670,7 +6682,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B232" t="n">
@@ -6699,7 +6711,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B233" t="n">
@@ -6728,7 +6740,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B234" t="n">
@@ -6757,32 +6769,32 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B235" t="n">
-        <v>165.6600036621094</v>
+        <v>165.3500061035156</v>
       </c>
       <c r="C235" t="n">
-        <v>165.6600036621094</v>
+        <v>165.3500061035156</v>
       </c>
       <c r="D235" t="n">
-        <v>87085100</v>
+        <v>92071000</v>
       </c>
       <c r="E235" t="n">
         <v>9.56</v>
       </c>
       <c r="F235" t="n">
-        <v>17.32845226591102</v>
+        <v>17.29602574304556</v>
       </c>
       <c r="G235" t="n">
         <v>1072671613</v>
       </c>
       <c r="H235" t="n">
-        <v>177698783337.8208</v>
+        <v>177366257756.618</v>
       </c>
       <c r="I235" t="n">
-        <v>0.08118523781611438</v>
+        <v>0.08583335187038273</v>
       </c>
     </row>
   </sheetData>
@@ -6814,75 +6826,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6918,13 +6930,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6960,13 +6972,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7002,13 +7014,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7044,13 +7056,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7086,13 +7098,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7119,7 +7131,7 @@
       <c r="I7" t="n">
         <v>1.08</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K7" t="n">
@@ -7132,13 +7144,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7165,7 +7177,7 @@
       <c r="I8" t="n">
         <v>1.26</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K8" t="n">
@@ -7178,13 +7190,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7211,7 +7223,7 @@
       <c r="I9" t="n">
         <v>1.28</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K9" t="n">
@@ -7224,13 +7236,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7257,7 +7269,7 @@
       <c r="I10" t="n">
         <v>1.22</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K10" t="n">
@@ -7270,13 +7282,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7303,7 +7315,7 @@
       <c r="I11" t="n">
         <v>1.64</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K11" t="n">
@@ -7316,13 +7328,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7349,7 +7361,7 @@
       <c r="I12" t="n">
         <v>1.46</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K12" t="n">
@@ -7362,13 +7374,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7395,7 +7407,7 @@
       <c r="I13" t="n">
         <v>1.82</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K13" t="n">
@@ -7408,13 +7420,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7441,7 +7453,7 @@
       <c r="I14" t="n">
         <v>2.48</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K14" t="n">
@@ -7454,13 +7466,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7487,7 +7499,7 @@
       <c r="I15" t="n">
         <v>2.16</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K15" t="n">
@@ -7500,13 +7512,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7533,7 +7545,7 @@
       <c r="I16" t="n">
         <v>2.14</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K16" t="n">
@@ -7546,13 +7558,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7579,7 +7591,7 @@
       <c r="I17" t="n">
         <v>1.3</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K17" t="n">
@@ -7592,13 +7604,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7625,7 +7637,7 @@
       <c r="I18" t="n">
         <v>0.21</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K18" t="n">
@@ -7638,13 +7650,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7671,7 +7683,7 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K19" t="n">
@@ -7684,13 +7696,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7717,7 +7729,7 @@
       <c r="I20" t="n">
         <v>-0.29</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K20" t="n">
@@ -7730,13 +7742,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7763,7 +7775,7 @@
       <c r="I21" t="n">
         <v>0.21</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K21" t="n">
@@ -7776,13 +7788,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7809,7 +7821,7 @@
       <c r="I22" t="n">
         <v>0.14</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="K22" t="n">
@@ -7822,13 +7834,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7855,7 +7867,7 @@
       <c r="I23" t="n">
         <v>0.2899999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K23" t="n">
@@ -7868,13 +7880,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7901,7 +7913,7 @@
       <c r="I24" t="n">
         <v>0.39</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K24" t="n">
@@ -7914,13 +7926,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7947,7 +7959,7 @@
       <c r="I25" t="n">
         <v>0.33</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K25" t="n">
@@ -7960,13 +7972,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7993,7 +8005,7 @@
       <c r="I26" t="n">
         <v>0.6</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K26" t="n">
@@ -8006,13 +8018,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8039,7 +8051,7 @@
       <c r="I27" t="n">
         <v>0.82</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="K27" t="n">
@@ -8052,13 +8064,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8085,7 +8097,7 @@
       <c r="I28" t="n">
         <v>1.47</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K28" t="n">
@@ -8098,13 +8110,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8131,7 +8143,7 @@
       <c r="I29" t="n">
         <v>1.3</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K29" t="n">
@@ -8144,13 +8156,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8177,7 +8189,7 @@
       <c r="I30" t="n">
         <v>1.57</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="K30" t="n">
@@ -8190,13 +8202,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8223,7 +8235,7 @@
       <c r="I31" t="n">
         <v>1.68</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="K31" t="n">
@@ -8236,13 +8248,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8269,7 +8281,7 @@
       <c r="I32" t="n">
         <v>1.92</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="K32" t="n">
@@ -8282,13 +8294,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8315,7 +8327,7 @@
       <c r="I33" t="n">
         <v>2.34</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="K33" t="n">
@@ -8328,13 +8340,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8361,7 +8373,7 @@
       <c r="I34" t="n">
         <v>2.55</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="K34" t="n">
@@ -8374,13 +8386,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8407,7 +8419,7 @@
       <c r="I35" t="n">
         <v>5.21</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K35" t="n">
@@ -8420,13 +8432,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8453,7 +8465,7 @@
       <c r="I36" t="n">
         <v>5.19</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K36" t="n">
@@ -8466,13 +8478,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8499,7 +8511,7 @@
       <c r="I37" t="n">
         <v>5.44</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K37" t="n">
@@ -8512,13 +8524,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8545,7 +8557,7 @@
       <c r="I38" t="n">
         <v>5.74</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K38" t="n">
@@ -8558,13 +8570,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8591,7 +8603,7 @@
       <c r="I39" t="n">
         <v>3.38</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K39" t="n">
@@ -8604,13 +8616,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8637,7 +8649,7 @@
       <c r="I40" t="n">
         <v>3.66</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K40" t="n">
@@ -8650,13 +8662,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8683,7 +8695,7 @@
       <c r="I41" t="n">
         <v>3.83</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K41" t="n">
@@ -8696,13 +8708,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8729,7 +8741,7 @@
       <c r="I42" t="n">
         <v>3.91</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="K42" t="n">
@@ -8742,13 +8754,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8775,7 +8787,7 @@
       <c r="I43" t="n">
         <v>4.03</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K43" t="n">
@@ -8788,13 +8800,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8821,7 +8833,7 @@
       <c r="I44" t="n">
         <v>4.07</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K44" t="n">
@@ -8834,13 +8846,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8867,7 +8879,7 @@
       <c r="I45" t="n">
         <v>3.07</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K45" t="n">
@@ -8880,13 +8892,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8913,7 +8925,7 @@
       <c r="I46" t="n">
         <v>3.06</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K46" t="n">
@@ -8926,13 +8938,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8959,7 +8971,7 @@
       <c r="I47" t="n">
         <v>2.79</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K47" t="n">
@@ -8972,13 +8984,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9005,7 +9017,7 @@
       <c r="I48" t="n">
         <v>2.43</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K48" t="n">
@@ -9018,13 +9030,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9051,7 +9063,7 @@
       <c r="I49" t="n">
         <v>3.12</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K49" t="n">
@@ -9064,13 +9076,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9097,7 +9109,7 @@
       <c r="I50" t="n">
         <v>2.67</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K50" t="n">
@@ -9110,13 +9122,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9143,7 +9155,7 @@
       <c r="I51" t="n">
         <v>2.41</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K51" t="n">
@@ -9156,13 +9168,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9189,7 +9201,7 @@
       <c r="I52" t="n">
         <v>2.24</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="K52" t="n">
@@ -9202,13 +9214,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9235,7 +9247,7 @@
       <c r="I53" t="n">
         <v>1.37</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K53" t="n">
@@ -9248,13 +9260,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9281,7 +9293,7 @@
       <c r="I54" t="n">
         <v>1.22</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K54" t="n">
@@ -9294,13 +9306,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9327,7 +9339,7 @@
       <c r="I55" t="n">
         <v>2.06</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K55" t="n">
@@ -9340,13 +9352,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9373,7 +9385,7 @@
       <c r="I56" t="n">
         <v>3.07</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K56" t="n">
@@ -9386,13 +9398,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9419,7 +9431,7 @@
       <c r="I57" t="n">
         <v>5.02</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K57" t="n">
@@ -9432,13 +9444,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9465,7 +9477,7 @@
       <c r="I58" t="n">
         <v>6.44</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K58" t="n">
@@ -9478,13 +9490,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9511,7 +9523,7 @@
       <c r="I59" t="n">
         <v>6.93</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K59" t="n">
@@ -9524,13 +9536,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9557,7 +9569,7 @@
       <c r="I60" t="n">
         <v>7.35</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K60" t="n">
@@ -9570,13 +9582,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9603,7 +9615,7 @@
       <c r="I61" t="n">
         <v>7.979999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K61" t="n">
@@ -9616,13 +9628,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9649,7 +9661,7 @@
       <c r="I62" t="n">
         <v>8.77</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K62" t="n">
@@ -9662,13 +9674,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9695,7 +9707,7 @@
       <c r="I63" t="n">
         <v>9.66</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K63" t="n">
@@ -9708,13 +9720,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9741,7 +9753,7 @@
       <c r="I64" t="n">
         <v>10.24</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K64" t="n">
@@ -9754,13 +9766,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9787,7 +9799,7 @@
       <c r="I65" t="n">
         <v>10.59</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K65" t="n">
@@ -9800,13 +9812,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9833,7 +9845,7 @@
       <c r="I66" t="n">
         <v>10.39</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K66" t="n">
@@ -9846,13 +9858,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9879,7 +9891,7 @@
       <c r="I67" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K67" t="n">
@@ -9892,13 +9904,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -9925,7 +9937,7 @@
       <c r="I68" t="n">
         <v>9.41</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K68" t="n">
@@ -9938,13 +9950,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -9971,7 +9983,7 @@
       <c r="I69" t="n">
         <v>9.56</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K69" t="n">
@@ -10008,52 +10020,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C2" t="n">
@@ -10082,10 +10094,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C3" t="n">
@@ -10114,10 +10126,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C4" t="n">
@@ -10146,10 +10158,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C5" t="n">
@@ -10178,10 +10190,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C6" t="n">
@@ -10210,10 +10222,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C7" t="n">
@@ -10242,10 +10254,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C8" t="n">
@@ -10274,10 +10286,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41022</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C9" t="n">
@@ -10306,10 +10318,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41110</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C10" t="n">
@@ -10338,10 +10350,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C11" t="n">
@@ -10370,10 +10382,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C12" t="n">
@@ -10402,10 +10414,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C13" t="n">
@@ -10434,10 +10446,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C14" t="n">
@@ -10466,10 +10478,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C15" t="n">
@@ -10498,10 +10510,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C16" t="n">
@@ -10530,10 +10542,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C17" t="n">
@@ -10562,10 +10574,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C18" t="n">
@@ -10594,10 +10606,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41935</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="C19" t="n">
@@ -10626,10 +10638,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42052</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C20" t="n">
@@ -10658,10 +10670,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C21" t="n">
@@ -10690,10 +10702,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C22" t="n">
@@ -10722,10 +10734,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C23" t="n">
@@ -10754,10 +10766,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42411</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="C24" t="n">
@@ -10786,10 +10798,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42481</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C25" t="n">
@@ -10818,10 +10830,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42572</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C26" t="n">
@@ -10850,10 +10862,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42663</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="C27" t="n">
@@ -10882,10 +10894,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42774</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="C28" t="n">
@@ -10914,10 +10926,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42844</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="C29" t="n">
@@ -10946,10 +10958,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="C30" t="n">
@@ -10978,10 +10990,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43027</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="C31" t="n">
@@ -11010,10 +11022,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C32" t="n">
@@ -11042,10 +11054,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C33" t="n">
@@ -11074,10 +11086,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C34" t="n">
@@ -11106,10 +11118,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43398</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C35" t="n">
@@ -11138,10 +11150,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43500</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C36" t="n">
@@ -11170,10 +11182,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C37" t="n">
@@ -11202,10 +11214,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C38" t="n">
@@ -11234,10 +11246,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43761</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="C39" t="n">
@@ -11266,10 +11278,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C40" t="n">
@@ -11298,10 +11310,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C41" t="n">
@@ -11330,10 +11342,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C42" t="n">
@@ -11362,10 +11374,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C43" t="n">
@@ -11394,10 +11406,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C44" t="n">
@@ -11426,10 +11438,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44314</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C45" t="n">
@@ -11458,10 +11470,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C46" t="n">
@@ -11490,10 +11502,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44496</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C47" t="n">
@@ -11522,10 +11534,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44599</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C48" t="n">
@@ -11554,10 +11566,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C49" t="n">
@@ -11586,10 +11598,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C50" t="n">
@@ -11618,10 +11630,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C51" t="n">
@@ -11650,10 +11662,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C52" t="n">
@@ -11682,10 +11694,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C53" t="n">
@@ -11714,10 +11726,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C54" t="n">
@@ -11746,10 +11758,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C55" t="n">
@@ -11778,10 +11790,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C56" t="n">
@@ -11810,10 +11822,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C57" t="n">
@@ -11842,10 +11854,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C58" t="n">
@@ -11874,10 +11886,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C59" t="n">
@@ -11906,10 +11918,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45681</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C60" t="n">
@@ -11938,10 +11950,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C61" t="n">
@@ -11970,10 +11982,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C62" t="n">
@@ -12002,10 +12014,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C63" t="n">
@@ -12034,10 +12046,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C64" t="n">
@@ -12066,10 +12078,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C65" t="n">
@@ -12098,10 +12110,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C66" t="n">
@@ -12148,12 +12160,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/TMUS.xlsx
+++ b/salidas/empresas/TMUS.xlsx
@@ -555,7 +555,7 @@
         <v>39294</v>
       </c>
       <c r="B5" t="n">
-        <v>57.69759750366211</v>
+        <v>57.69760131835938</v>
       </c>
       <c r="C5" t="n">
         <v>73.23999786376953</v>
@@ -593,7 +593,7 @@
         <v>39355</v>
       </c>
       <c r="B7" t="n">
-        <v>42.98172378540039</v>
+        <v>42.98171997070312</v>
       </c>
       <c r="C7" t="n">
         <v>54.56000137329102</v>
@@ -612,7 +612,7 @@
         <v>39386</v>
       </c>
       <c r="B8" t="n">
-        <v>35.45045852661133</v>
+        <v>35.45046615600586</v>
       </c>
       <c r="C8" t="n">
         <v>45</v>
@@ -669,7 +669,7 @@
         <v>39478</v>
       </c>
       <c r="B11" t="n">
-        <v>28.64397430419922</v>
+        <v>28.64398193359375</v>
       </c>
       <c r="C11" t="n">
         <v>36.36000061035156</v>
@@ -688,7 +688,7 @@
         <v>39507</v>
       </c>
       <c r="B12" t="n">
-        <v>25.13043785095215</v>
+        <v>25.13043975830078</v>
       </c>
       <c r="C12" t="n">
         <v>31.89999961853027</v>
@@ -726,7 +726,7 @@
         <v>39568</v>
       </c>
       <c r="B14" t="n">
-        <v>30.94431304931641</v>
+        <v>30.9443187713623</v>
       </c>
       <c r="C14" t="n">
         <v>39.27999877929688</v>
@@ -745,7 +745,7 @@
         <v>39599</v>
       </c>
       <c r="B15" t="n">
-        <v>33.46523666381836</v>
+        <v>33.46523284912109</v>
       </c>
       <c r="C15" t="n">
         <v>42.47999954223633</v>
@@ -764,7 +764,7 @@
         <v>39629</v>
       </c>
       <c r="B16" t="n">
-        <v>27.90345191955566</v>
+        <v>27.90345001220703</v>
       </c>
       <c r="C16" t="n">
         <v>35.41999816894531</v>
@@ -783,7 +783,7 @@
         <v>39660</v>
       </c>
       <c r="B17" t="n">
-        <v>26.20182991027832</v>
+        <v>26.20183181762695</v>
       </c>
       <c r="C17" t="n">
         <v>33.2599983215332</v>
@@ -802,7 +802,7 @@
         <v>39691</v>
       </c>
       <c r="B18" t="n">
-        <v>26.5799732208252</v>
+        <v>26.57997131347656</v>
       </c>
       <c r="C18" t="n">
         <v>33.7400016784668</v>
@@ -821,7 +821,7 @@
         <v>39721</v>
       </c>
       <c r="B19" t="n">
-        <v>22.04231071472168</v>
+        <v>22.04230880737305</v>
       </c>
       <c r="C19" t="n">
         <v>27.97999954223633</v>
@@ -840,7 +840,7 @@
         <v>39752</v>
       </c>
       <c r="B20" t="n">
-        <v>21.64841842651367</v>
+        <v>21.64841651916504</v>
       </c>
       <c r="C20" t="n">
         <v>27.47999954223633</v>
@@ -859,7 +859,7 @@
         <v>39782</v>
       </c>
       <c r="B21" t="n">
-        <v>23.06643295288086</v>
+        <v>23.06643486022949</v>
       </c>
       <c r="C21" t="n">
         <v>29.28000068664551</v>
@@ -916,7 +916,7 @@
         <v>39872</v>
       </c>
       <c r="B24" t="n">
-        <v>22.84585189819336</v>
+        <v>22.84585571289062</v>
       </c>
       <c r="C24" t="n">
         <v>29</v>
@@ -954,7 +954,7 @@
         <v>39933</v>
       </c>
       <c r="B26" t="n">
-        <v>26.92659759521484</v>
+        <v>26.92659187316895</v>
       </c>
       <c r="C26" t="n">
         <v>34.18000030517578</v>
@@ -1011,7 +1011,7 @@
         <v>40025</v>
       </c>
       <c r="B29" t="n">
-        <v>18.67058181762695</v>
+        <v>18.67057991027832</v>
       </c>
       <c r="C29" t="n">
         <v>23.70000076293945</v>
@@ -1030,7 +1030,7 @@
         <v>40056</v>
       </c>
       <c r="B30" t="n">
-        <v>12.54158687591553</v>
+        <v>12.54158496856689</v>
       </c>
       <c r="C30" t="n">
         <v>15.92000007629395</v>
@@ -1068,7 +1068,7 @@
         <v>40117</v>
       </c>
       <c r="B32" t="n">
-        <v>9.815840721130371</v>
+        <v>9.815838813781738</v>
       </c>
       <c r="C32" t="n">
         <v>12.46000003814697</v>
@@ -1125,7 +1125,7 @@
         <v>40209</v>
       </c>
       <c r="B35" t="n">
-        <v>8.870494842529297</v>
+        <v>8.870492935180664</v>
       </c>
       <c r="C35" t="n">
         <v>11.26000022888184</v>
@@ -1144,7 +1144,7 @@
         <v>40237</v>
       </c>
       <c r="B36" t="n">
-        <v>9.721304893493652</v>
+        <v>9.721305847167969</v>
       </c>
       <c r="C36" t="n">
         <v>12.34000015258789</v>
@@ -1201,7 +1201,7 @@
         <v>40329</v>
       </c>
       <c r="B39" t="n">
-        <v>14.16443061828613</v>
+        <v>14.16442966461182</v>
       </c>
       <c r="C39" t="n">
         <v>17.97999954223633</v>
@@ -1220,7 +1220,7 @@
         <v>40359</v>
       </c>
       <c r="B40" t="n">
-        <v>12.90396785736084</v>
+        <v>12.90396881103516</v>
       </c>
       <c r="C40" t="n">
         <v>16.3799991607666</v>
@@ -1239,7 +1239,7 @@
         <v>40390</v>
       </c>
       <c r="B41" t="n">
-        <v>14.10140705108643</v>
+        <v>14.10140800476074</v>
       </c>
       <c r="C41" t="n">
         <v>17.89999961853027</v>
@@ -1258,7 +1258,7 @@
         <v>40421</v>
       </c>
       <c r="B42" t="n">
-        <v>14.08564949035645</v>
+        <v>14.08565235137939</v>
       </c>
       <c r="C42" t="n">
         <v>17.8799991607666</v>
@@ -1283,7 +1283,7 @@
         <v>40451</v>
       </c>
       <c r="B43" t="n">
-        <v>16.48052787780762</v>
+        <v>16.48052978515625</v>
       </c>
       <c r="C43" t="n">
         <v>20.92000007629395</v>
@@ -1333,7 +1333,7 @@
         <v>40512</v>
       </c>
       <c r="B45" t="n">
-        <v>19.14325141906738</v>
+        <v>19.14324951171875</v>
       </c>
       <c r="C45" t="n">
         <v>24.29999923706055</v>
@@ -1358,7 +1358,7 @@
         <v>40543</v>
       </c>
       <c r="B46" t="n">
-        <v>19.89952850341797</v>
+        <v>19.8995246887207</v>
       </c>
       <c r="C46" t="n">
         <v>25.26000022888184</v>
@@ -1383,7 +1383,7 @@
         <v>40574</v>
       </c>
       <c r="B47" t="n">
-        <v>20.37220573425293</v>
+        <v>20.37220191955566</v>
       </c>
       <c r="C47" t="n">
         <v>25.86000061035156</v>
@@ -1408,7 +1408,7 @@
         <v>40602</v>
       </c>
       <c r="B48" t="n">
-        <v>22.68829154968262</v>
+        <v>22.68829917907715</v>
       </c>
       <c r="C48" t="n">
         <v>28.79999923706055</v>
@@ -1433,7 +1433,7 @@
         <v>40633</v>
       </c>
       <c r="B49" t="n">
-        <v>25.58735466003418</v>
+        <v>25.58735847473145</v>
       </c>
       <c r="C49" t="n">
         <v>32.47999954223633</v>
@@ -1483,7 +1483,7 @@
         <v>40694</v>
       </c>
       <c r="B51" t="n">
-        <v>28.20281410217285</v>
+        <v>28.20281600952148</v>
       </c>
       <c r="C51" t="n">
         <v>35.79999923706055</v>
@@ -1508,7 +1508,7 @@
         <v>40724</v>
       </c>
       <c r="B52" t="n">
-        <v>27.11566734313965</v>
+        <v>27.11566543579102</v>
       </c>
       <c r="C52" t="n">
         <v>34.41999816894531</v>
@@ -1533,7 +1533,7 @@
         <v>40755</v>
       </c>
       <c r="B53" t="n">
-        <v>25.65038108825684</v>
+        <v>25.6503849029541</v>
       </c>
       <c r="C53" t="n">
         <v>32.56000137329102</v>
@@ -1558,7 +1558,7 @@
         <v>40786</v>
       </c>
       <c r="B54" t="n">
-        <v>17.58342933654785</v>
+        <v>17.58343124389648</v>
       </c>
       <c r="C54" t="n">
         <v>22.31999969482422</v>
@@ -1583,7 +1583,7 @@
         <v>40816</v>
       </c>
       <c r="B55" t="n">
-        <v>13.72326946258545</v>
+        <v>13.72326850891113</v>
       </c>
       <c r="C55" t="n">
         <v>17.42000007629395</v>
@@ -1633,7 +1633,7 @@
         <v>40877</v>
       </c>
       <c r="B57" t="n">
-        <v>13.20332908630371</v>
+        <v>13.20333194732666</v>
       </c>
       <c r="C57" t="n">
         <v>16.76000022888184</v>
@@ -1683,7 +1683,7 @@
         <v>40939</v>
       </c>
       <c r="B59" t="n">
-        <v>13.92809391021729</v>
+        <v>13.92809200286865</v>
       </c>
       <c r="C59" t="n">
         <v>17.68000030517578</v>
@@ -1737,7 +1737,7 @@
         <v>40999</v>
       </c>
       <c r="B61" t="n">
-        <v>14.21169757843018</v>
+        <v>14.21169853210449</v>
       </c>
       <c r="C61" t="n">
         <v>18.04000091552734</v>
@@ -1766,7 +1766,7 @@
         <v>41029</v>
       </c>
       <c r="B62" t="n">
-        <v>11.50170803070068</v>
+        <v>11.50170612335205</v>
       </c>
       <c r="C62" t="n">
         <v>14.60000038146973</v>
@@ -1795,7 +1795,7 @@
         <v>41060</v>
       </c>
       <c r="B63" t="n">
-        <v>10.08368873596191</v>
+        <v>10.08368587493896</v>
       </c>
       <c r="C63" t="n">
         <v>12.80000019073486</v>
@@ -1824,7 +1824,7 @@
         <v>41090</v>
       </c>
       <c r="B64" t="n">
-        <v>9.532234191894531</v>
+        <v>9.53223705291748</v>
       </c>
       <c r="C64" t="n">
         <v>12.10000038146973</v>
@@ -1853,7 +1853,7 @@
         <v>41121</v>
       </c>
       <c r="B65" t="n">
-        <v>13.80204772949219</v>
+        <v>13.80204582214355</v>
       </c>
       <c r="C65" t="n">
         <v>17.52000045776367</v>
@@ -1882,7 +1882,7 @@
         <v>41152</v>
       </c>
       <c r="B66" t="n">
-        <v>15.33035564422607</v>
+        <v>15.33035373687744</v>
       </c>
       <c r="C66" t="n">
         <v>19.45999908447266</v>
@@ -1940,7 +1940,7 @@
         <v>41213</v>
       </c>
       <c r="B68" t="n">
-        <v>16.08663177490234</v>
+        <v>16.08662986755371</v>
       </c>
       <c r="C68" t="n">
         <v>20.42000007629395</v>
@@ -1969,7 +1969,7 @@
         <v>41243</v>
       </c>
       <c r="B69" t="n">
-        <v>16.77988624572754</v>
+        <v>16.77988433837891</v>
       </c>
       <c r="C69" t="n">
         <v>21.29999923706055</v>
@@ -1998,7 +1998,7 @@
         <v>41274</v>
       </c>
       <c r="B70" t="n">
-        <v>15.66122722625732</v>
+        <v>15.66122531890869</v>
       </c>
       <c r="C70" t="n">
         <v>19.8799991607666</v>
@@ -2027,7 +2027,7 @@
         <v>41305</v>
       </c>
       <c r="B71" t="n">
-        <v>15.80302619934082</v>
+        <v>15.80302715301514</v>
       </c>
       <c r="C71" t="n">
         <v>20.05999946594238</v>
@@ -2056,7 +2056,7 @@
         <v>41333</v>
       </c>
       <c r="B72" t="n">
-        <v>15.44064712524414</v>
+        <v>15.44064998626709</v>
       </c>
       <c r="C72" t="n">
         <v>19.60000038146973</v>
@@ -2085,7 +2085,7 @@
         <v>41364</v>
       </c>
       <c r="B73" t="n">
-        <v>17.17377662658691</v>
+        <v>17.17378044128418</v>
       </c>
       <c r="C73" t="n">
         <v>21.79999923706055</v>
@@ -2114,7 +2114,7 @@
         <v>41394</v>
       </c>
       <c r="B74" t="n">
-        <v>18.65482139587402</v>
+        <v>18.65482521057129</v>
       </c>
       <c r="C74" t="n">
         <v>23.68000030517578</v>
@@ -2143,7 +2143,7 @@
         <v>41425</v>
       </c>
       <c r="B75" t="n">
-        <v>20.37578201293945</v>
+        <v>20.37578392028809</v>
       </c>
       <c r="C75" t="n">
         <v>21.43000030517578</v>
@@ -2172,7 +2172,7 @@
         <v>41455</v>
       </c>
       <c r="B76" t="n">
-        <v>23.58950996398926</v>
+        <v>23.58950805664062</v>
       </c>
       <c r="C76" t="n">
         <v>24.80999946594238</v>
@@ -2259,7 +2259,7 @@
         <v>41547</v>
       </c>
       <c r="B79" t="n">
-        <v>24.69244194030762</v>
+        <v>24.69244003295898</v>
       </c>
       <c r="C79" t="n">
         <v>25.96999931335449</v>
@@ -2288,7 +2288,7 @@
         <v>41578</v>
       </c>
       <c r="B80" t="n">
-        <v>26.3658618927002</v>
+        <v>26.36585807800293</v>
       </c>
       <c r="C80" t="n">
         <v>27.72999954223633</v>
@@ -2317,7 +2317,7 @@
         <v>41608</v>
       </c>
       <c r="B81" t="n">
-        <v>24.73047256469727</v>
+        <v>24.7304744720459</v>
       </c>
       <c r="C81" t="n">
         <v>26.01000022888184</v>
@@ -2375,7 +2375,7 @@
         <v>41670</v>
       </c>
       <c r="B83" t="n">
-        <v>29.06615257263184</v>
+        <v>29.0661506652832</v>
       </c>
       <c r="C83" t="n">
         <v>30.56999969482422</v>
@@ -2404,7 +2404,7 @@
         <v>41698</v>
       </c>
       <c r="B84" t="n">
-        <v>28.99959564208984</v>
+        <v>28.99959754943848</v>
       </c>
       <c r="C84" t="n">
         <v>30.5</v>
@@ -2431,7 +2431,7 @@
         <v>41729</v>
       </c>
       <c r="B85" t="n">
-        <v>31.40513610839844</v>
+        <v>31.4051342010498</v>
       </c>
       <c r="C85" t="n">
         <v>33.02999877929688</v>
@@ -2458,7 +2458,7 @@
         <v>41759</v>
       </c>
       <c r="B86" t="n">
-        <v>27.84912490844727</v>
+        <v>27.84912300109863</v>
       </c>
       <c r="C86" t="n">
         <v>29.29000091552734</v>
@@ -2485,7 +2485,7 @@
         <v>41790</v>
       </c>
       <c r="B87" t="n">
-        <v>32.64117813110352</v>
+        <v>32.64118194580078</v>
       </c>
       <c r="C87" t="n">
         <v>34.33000183105469</v>
@@ -2512,7 +2512,7 @@
         <v>41820</v>
       </c>
       <c r="B88" t="n">
-        <v>31.96611213684082</v>
+        <v>31.96610832214355</v>
       </c>
       <c r="C88" t="n">
         <v>33.61999893188477</v>
@@ -2539,7 +2539,7 @@
         <v>41851</v>
       </c>
       <c r="B89" t="n">
-        <v>31.31956481933594</v>
+        <v>31.31955718994141</v>
       </c>
       <c r="C89" t="n">
         <v>32.93999862670898</v>
@@ -2626,7 +2626,7 @@
         <v>41943</v>
       </c>
       <c r="B92" t="n">
-        <v>27.75403785705566</v>
+        <v>27.7540397644043</v>
       </c>
       <c r="C92" t="n">
         <v>29.19000053405762</v>
@@ -2655,7 +2655,7 @@
         <v>41973</v>
       </c>
       <c r="B93" t="n">
-        <v>27.75403785705566</v>
+        <v>27.7540397644043</v>
       </c>
       <c r="C93" t="n">
         <v>29.19000053405762</v>
@@ -2684,7 +2684,7 @@
         <v>42004</v>
       </c>
       <c r="B94" t="n">
-        <v>25.61472511291504</v>
+        <v>25.61472320556641</v>
       </c>
       <c r="C94" t="n">
         <v>26.94000053405762</v>
@@ -2713,7 +2713,7 @@
         <v>42035</v>
       </c>
       <c r="B95" t="n">
-        <v>28.69533920288086</v>
+        <v>28.69533729553223</v>
       </c>
       <c r="C95" t="n">
         <v>30.18000030517578</v>
@@ -2742,7 +2742,7 @@
         <v>42063</v>
       </c>
       <c r="B96" t="n">
-        <v>31.40513610839844</v>
+        <v>31.4051342010498</v>
       </c>
       <c r="C96" t="n">
         <v>33.02999877929688</v>
@@ -2800,7 +2800,7 @@
         <v>42124</v>
       </c>
       <c r="B98" t="n">
-        <v>32.36545181274414</v>
+        <v>32.36545944213867</v>
       </c>
       <c r="C98" t="n">
         <v>34.04000091552734</v>
@@ -2858,7 +2858,7 @@
         <v>42185</v>
       </c>
       <c r="B100" t="n">
-        <v>36.86276626586914</v>
+        <v>36.86275863647461</v>
       </c>
       <c r="C100" t="n">
         <v>38.77000045776367</v>
@@ -2916,7 +2916,7 @@
         <v>42247</v>
       </c>
       <c r="B102" t="n">
-        <v>37.66143417358398</v>
+        <v>37.66144943237305</v>
       </c>
       <c r="C102" t="n">
         <v>39.61000061035156</v>
@@ -3003,7 +3003,7 @@
         <v>42338</v>
       </c>
       <c r="B105" t="n">
-        <v>33.75362396240234</v>
+        <v>33.75363159179688</v>
       </c>
       <c r="C105" t="n">
         <v>35.5</v>
@@ -3032,7 +3032,7 @@
         <v>42369</v>
       </c>
       <c r="B106" t="n">
-        <v>37.19555282592773</v>
+        <v>37.19554138183594</v>
       </c>
       <c r="C106" t="n">
         <v>39.11999893188477</v>
@@ -3090,7 +3090,7 @@
         <v>42429</v>
       </c>
       <c r="B108" t="n">
-        <v>35.27491760253906</v>
+        <v>35.2749137878418</v>
       </c>
       <c r="C108" t="n">
         <v>37.09999847412109</v>
@@ -3119,7 +3119,7 @@
         <v>42460</v>
       </c>
       <c r="B109" t="n">
-        <v>36.4158821105957</v>
+        <v>36.41588973999023</v>
       </c>
       <c r="C109" t="n">
         <v>38.29999923706055</v>
@@ -3148,7 +3148,7 @@
         <v>42490</v>
       </c>
       <c r="B110" t="n">
-        <v>37.34767150878906</v>
+        <v>37.34768295288086</v>
       </c>
       <c r="C110" t="n">
         <v>39.27999877929688</v>
@@ -3177,7 +3177,7 @@
         <v>42521</v>
       </c>
       <c r="B111" t="n">
-        <v>40.65648651123047</v>
+        <v>40.65649032592773</v>
       </c>
       <c r="C111" t="n">
         <v>42.7599983215332</v>
@@ -3206,7 +3206,7 @@
         <v>42551</v>
       </c>
       <c r="B112" t="n">
-        <v>41.14139175415039</v>
+        <v>41.14139556884766</v>
       </c>
       <c r="C112" t="n">
         <v>43.27000045776367</v>
@@ -3235,7 +3235,7 @@
         <v>42582</v>
       </c>
       <c r="B113" t="n">
-        <v>44.06037139892578</v>
+        <v>44.06037521362305</v>
       </c>
       <c r="C113" t="n">
         <v>46.34000015258789</v>
@@ -3264,7 +3264,7 @@
         <v>42613</v>
       </c>
       <c r="B114" t="n">
-        <v>44.06037139892578</v>
+        <v>44.06037521362305</v>
       </c>
       <c r="C114" t="n">
         <v>46.34000015258789</v>
@@ -3293,7 +3293,7 @@
         <v>42643</v>
       </c>
       <c r="B115" t="n">
-        <v>44.42167282104492</v>
+        <v>44.42167663574219</v>
       </c>
       <c r="C115" t="n">
         <v>46.72000122070312</v>
@@ -3351,7 +3351,7 @@
         <v>42704</v>
       </c>
       <c r="B117" t="n">
-        <v>51.54320526123047</v>
+        <v>51.5432243347168</v>
       </c>
       <c r="C117" t="n">
         <v>54.20999908447266</v>
@@ -3438,7 +3438,7 @@
         <v>42794</v>
       </c>
       <c r="B120" t="n">
-        <v>59.45393371582031</v>
+        <v>59.45392990112305</v>
       </c>
       <c r="C120" t="n">
         <v>62.52999877929688</v>
@@ -3554,7 +3554,7 @@
         <v>42916</v>
       </c>
       <c r="B124" t="n">
-        <v>57.63788604736328</v>
+        <v>57.63788223266602</v>
       </c>
       <c r="C124" t="n">
         <v>60.61999893188477</v>
@@ -3583,7 +3583,7 @@
         <v>42947</v>
       </c>
       <c r="B125" t="n">
-        <v>58.62672424316406</v>
+        <v>58.62672805786133</v>
       </c>
       <c r="C125" t="n">
         <v>61.65999984741211</v>
@@ -3612,7 +3612,7 @@
         <v>42978</v>
       </c>
       <c r="B126" t="n">
-        <v>61.52668380737305</v>
+        <v>61.52667999267578</v>
       </c>
       <c r="C126" t="n">
         <v>64.70999908447266</v>
@@ -3641,7 +3641,7 @@
         <v>43008</v>
       </c>
       <c r="B127" t="n">
-        <v>58.62672424316406</v>
+        <v>58.62672805786133</v>
       </c>
       <c r="C127" t="n">
         <v>61.65999984741211</v>
@@ -3728,7 +3728,7 @@
         <v>43100</v>
       </c>
       <c r="B130" t="n">
-        <v>60.38571929931641</v>
+        <v>60.38571166992188</v>
       </c>
       <c r="C130" t="n">
         <v>63.5099983215332</v>
@@ -3815,7 +3815,7 @@
         <v>43190</v>
       </c>
       <c r="B133" t="n">
-        <v>58.03722381591797</v>
+        <v>58.03722763061523</v>
       </c>
       <c r="C133" t="n">
         <v>61.04000091552734</v>
@@ -3931,7 +3931,7 @@
         <v>43312</v>
       </c>
       <c r="B137" t="n">
-        <v>57.04838562011719</v>
+        <v>57.04838180541992</v>
       </c>
       <c r="C137" t="n">
         <v>60</v>
@@ -3960,7 +3960,7 @@
         <v>43343</v>
       </c>
       <c r="B138" t="n">
-        <v>62.79125595092773</v>
+        <v>62.79125213623047</v>
       </c>
       <c r="C138" t="n">
         <v>66.04000091552734</v>
@@ -4047,7 +4047,7 @@
         <v>43434</v>
       </c>
       <c r="B141" t="n">
-        <v>65.08270263671875</v>
+        <v>65.08269500732422</v>
       </c>
       <c r="C141" t="n">
         <v>68.44999694824219</v>
@@ -4105,7 +4105,7 @@
         <v>43496</v>
       </c>
       <c r="B143" t="n">
-        <v>66.19514465332031</v>
+        <v>66.19513702392578</v>
       </c>
       <c r="C143" t="n">
         <v>69.62000274658203</v>
@@ -4134,7 +4134,7 @@
         <v>43524</v>
       </c>
       <c r="B144" t="n">
-        <v>68.65773010253906</v>
+        <v>68.65772247314453</v>
       </c>
       <c r="C144" t="n">
         <v>72.20999908447266</v>
@@ -4163,7 +4163,7 @@
         <v>43555</v>
       </c>
       <c r="B145" t="n">
-        <v>65.70072174072266</v>
+        <v>65.70071411132812</v>
       </c>
       <c r="C145" t="n">
         <v>69.09999847412109</v>
@@ -4221,7 +4221,7 @@
         <v>43616</v>
       </c>
       <c r="B147" t="n">
-        <v>69.82722473144531</v>
+        <v>69.82723236083984</v>
       </c>
       <c r="C147" t="n">
         <v>73.44000244140625</v>
@@ -4279,7 +4279,7 @@
         <v>43677</v>
       </c>
       <c r="B149" t="n">
-        <v>75.80779266357422</v>
+        <v>75.80780029296875</v>
       </c>
       <c r="C149" t="n">
         <v>79.73000335693359</v>
@@ -4337,7 +4337,7 @@
         <v>43738</v>
       </c>
       <c r="B151" t="n">
-        <v>74.89501953125</v>
+        <v>74.89502716064453</v>
       </c>
       <c r="C151" t="n">
         <v>78.76999664306641</v>
@@ -4366,7 +4366,7 @@
         <v>43769</v>
       </c>
       <c r="B152" t="n">
-        <v>78.59366607666016</v>
+        <v>78.59365844726562</v>
       </c>
       <c r="C152" t="n">
         <v>82.66000366210938</v>
@@ -4395,7 +4395,7 @@
         <v>43799</v>
       </c>
       <c r="B153" t="n">
-        <v>74.68584442138672</v>
+        <v>74.68585205078125</v>
       </c>
       <c r="C153" t="n">
         <v>78.55000305175781</v>
@@ -4424,7 +4424,7 @@
         <v>43830</v>
       </c>
       <c r="B154" t="n">
-        <v>74.56224822998047</v>
+        <v>74.56224060058594</v>
       </c>
       <c r="C154" t="n">
         <v>78.41999816894531</v>
@@ -4482,7 +4482,7 @@
         <v>43890</v>
       </c>
       <c r="B156" t="n">
-        <v>85.72471618652344</v>
+        <v>85.72470855712891</v>
       </c>
       <c r="C156" t="n">
         <v>90.16000366210938</v>
@@ -4511,7 +4511,7 @@
         <v>43921</v>
       </c>
       <c r="B157" t="n">
-        <v>79.77265930175781</v>
+        <v>79.77266693115234</v>
       </c>
       <c r="C157" t="n">
         <v>83.90000152587891</v>
@@ -4540,7 +4540,7 @@
         <v>43951</v>
       </c>
       <c r="B158" t="n">
-        <v>83.48080444335938</v>
+        <v>83.48081207275391</v>
       </c>
       <c r="C158" t="n">
         <v>87.80000305175781</v>
@@ -4569,7 +4569,7 @@
         <v>43982</v>
       </c>
       <c r="B159" t="n">
-        <v>95.11866760253906</v>
+        <v>95.11867523193359</v>
       </c>
       <c r="C159" t="n">
         <v>100.0400009155273</v>
@@ -4598,7 +4598,7 @@
         <v>44012</v>
       </c>
       <c r="B160" t="n">
-        <v>99.02648162841797</v>
+        <v>99.0264892578125</v>
       </c>
       <c r="C160" t="n">
         <v>104.1500015258789</v>
@@ -4685,7 +4685,7 @@
         <v>44104</v>
       </c>
       <c r="B163" t="n">
-        <v>108.7342300415039</v>
+        <v>108.7342224121094</v>
       </c>
       <c r="C163" t="n">
         <v>114.3600006103516</v>
@@ -4743,7 +4743,7 @@
         <v>44165</v>
       </c>
       <c r="B165" t="n">
-        <v>126.4002075195312</v>
+        <v>126.4002151489258</v>
       </c>
       <c r="C165" t="n">
         <v>132.9400024414062</v>
@@ -4888,7 +4888,7 @@
         <v>44316</v>
       </c>
       <c r="B170" t="n">
-        <v>125.6300506591797</v>
+        <v>125.6300430297852</v>
       </c>
       <c r="C170" t="n">
         <v>132.1300048828125</v>
@@ -4917,7 +4917,7 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>134.4915618896484</v>
+        <v>134.4915771484375</v>
       </c>
       <c r="C171" t="n">
         <v>141.4499969482422</v>
@@ -5004,7 +5004,7 @@
         <v>44439</v>
       </c>
       <c r="B174" t="n">
-        <v>130.2795104980469</v>
+        <v>130.2794799804688</v>
       </c>
       <c r="C174" t="n">
         <v>137.0200042724609</v>
@@ -5033,7 +5033,7 @@
         <v>44469</v>
       </c>
       <c r="B175" t="n">
-        <v>121.4750442504883</v>
+        <v>121.4750289916992</v>
       </c>
       <c r="C175" t="n">
         <v>127.7600021362305</v>
@@ -5062,7 +5062,7 @@
         <v>44500</v>
       </c>
       <c r="B176" t="n">
-        <v>109.3712692260742</v>
+        <v>109.3712539672852</v>
       </c>
       <c r="C176" t="n">
         <v>115.0299987792969</v>
@@ -5120,7 +5120,7 @@
         <v>44561</v>
       </c>
       <c r="B178" t="n">
-        <v>110.274528503418</v>
+        <v>110.2745208740234</v>
       </c>
       <c r="C178" t="n">
         <v>115.9800033569336</v>
@@ -5149,7 +5149,7 @@
         <v>44592</v>
       </c>
       <c r="B179" t="n">
-        <v>102.8487167358398</v>
+        <v>102.8487243652344</v>
       </c>
       <c r="C179" t="n">
         <v>108.1699981689453</v>
@@ -5178,7 +5178,7 @@
         <v>44620</v>
       </c>
       <c r="B180" t="n">
-        <v>117.1488571166992</v>
+        <v>117.1488494873047</v>
       </c>
       <c r="C180" t="n">
         <v>123.2099990844727</v>
@@ -5207,7 +5207,7 @@
         <v>44651</v>
       </c>
       <c r="B181" t="n">
-        <v>122.0360107421875</v>
+        <v>122.0359954833984</v>
       </c>
       <c r="C181" t="n">
         <v>128.3500061035156</v>
@@ -5236,7 +5236,7 @@
         <v>44681</v>
       </c>
       <c r="B182" t="n">
-        <v>117.0823059082031</v>
+        <v>117.0822982788086</v>
       </c>
       <c r="C182" t="n">
         <v>123.1399993896484</v>
@@ -5265,7 +5265,7 @@
         <v>44712</v>
       </c>
       <c r="B183" t="n">
-        <v>126.7329635620117</v>
+        <v>126.7329940795898</v>
       </c>
       <c r="C183" t="n">
         <v>133.2899932861328</v>
@@ -5323,7 +5323,7 @@
         <v>44773</v>
       </c>
       <c r="B185" t="n">
-        <v>136.0223693847656</v>
+        <v>136.0223999023438</v>
       </c>
       <c r="C185" t="n">
         <v>143.0599975585938</v>
@@ -5468,7 +5468,7 @@
         <v>44926</v>
       </c>
       <c r="B190" t="n">
-        <v>133.1128845214844</v>
+        <v>133.1128997802734</v>
       </c>
       <c r="C190" t="n">
         <v>140</v>
@@ -5497,7 +5497,7 @@
         <v>44957</v>
       </c>
       <c r="B191" t="n">
-        <v>141.9648895263672</v>
+        <v>141.9649047851562</v>
       </c>
       <c r="C191" t="n">
         <v>149.3099975585938</v>
@@ -5526,7 +5526,7 @@
         <v>44985</v>
       </c>
       <c r="B192" t="n">
-        <v>135.1856384277344</v>
+        <v>135.1856231689453</v>
       </c>
       <c r="C192" t="n">
         <v>142.1799926757812</v>
@@ -5555,7 +5555,7 @@
         <v>45016</v>
       </c>
       <c r="B193" t="n">
-        <v>137.7147827148438</v>
+        <v>137.7147979736328</v>
       </c>
       <c r="C193" t="n">
         <v>144.8399963378906</v>
@@ -5642,7 +5642,7 @@
         <v>45107</v>
       </c>
       <c r="B196" t="n">
-        <v>132.0669860839844</v>
+        <v>132.0670013427734</v>
       </c>
       <c r="C196" t="n">
         <v>138.8999938964844</v>
@@ -5700,7 +5700,7 @@
         <v>45169</v>
       </c>
       <c r="B198" t="n">
-        <v>129.5473480224609</v>
+        <v>129.5473937988281</v>
       </c>
       <c r="C198" t="n">
         <v>136.25</v>
@@ -5729,7 +5729,7 @@
         <v>45199</v>
       </c>
       <c r="B199" t="n">
-        <v>133.1604156494141</v>
+        <v>133.1604309082031</v>
       </c>
       <c r="C199" t="n">
         <v>140.0500030517578</v>
@@ -5758,7 +5758,7 @@
         <v>45230</v>
       </c>
       <c r="B200" t="n">
-        <v>136.7829895019531</v>
+        <v>136.7830047607422</v>
       </c>
       <c r="C200" t="n">
         <v>143.8600006103516</v>
@@ -5787,7 +5787,7 @@
         <v>45260</v>
       </c>
       <c r="B201" t="n">
-        <v>143.6732940673828</v>
+        <v>143.6732788085938</v>
       </c>
       <c r="C201" t="n">
         <v>150.4499969482422</v>
@@ -5874,7 +5874,7 @@
         <v>45351</v>
       </c>
       <c r="B204" t="n">
-        <v>156.5657806396484</v>
+        <v>156.5657958984375</v>
       </c>
       <c r="C204" t="n">
         <v>163.3000030517578</v>
@@ -5903,7 +5903,7 @@
         <v>45382</v>
       </c>
       <c r="B205" t="n">
-        <v>156.4890594482422</v>
+        <v>156.4890747070312</v>
       </c>
       <c r="C205" t="n">
         <v>163.2200012207031</v>
@@ -5932,7 +5932,7 @@
         <v>45412</v>
       </c>
       <c r="B206" t="n">
-        <v>157.3998870849609</v>
+        <v>157.3998718261719</v>
       </c>
       <c r="C206" t="n">
         <v>164.1699981689453</v>
@@ -5990,7 +5990,7 @@
         <v>45473</v>
       </c>
       <c r="B208" t="n">
-        <v>169.5602569580078</v>
+        <v>169.560302734375</v>
       </c>
       <c r="C208" t="n">
         <v>176.1799926757812</v>
@@ -6164,7 +6164,7 @@
         <v>45657</v>
       </c>
       <c r="B214" t="n">
-        <v>213.8972930908203</v>
+        <v>213.8973083496094</v>
       </c>
       <c r="C214" t="n">
         <v>220.7299957275391</v>
@@ -6193,7 +6193,7 @@
         <v>45688</v>
       </c>
       <c r="B215" t="n">
-        <v>225.7584381103516</v>
+        <v>225.7584228515625</v>
       </c>
       <c r="C215" t="n">
         <v>232.9700012207031</v>
@@ -6251,7 +6251,7 @@
         <v>45747</v>
       </c>
       <c r="B217" t="n">
-        <v>259.3178100585938</v>
+        <v>259.3177795410156</v>
       </c>
       <c r="C217" t="n">
         <v>266.7099914550781</v>
@@ -6338,7 +6338,7 @@
         <v>45838</v>
       </c>
       <c r="B220" t="n">
-        <v>232.5113983154297</v>
+        <v>232.5113677978516</v>
       </c>
       <c r="C220" t="n">
         <v>238.2599945068359</v>
@@ -6425,7 +6425,7 @@
         <v>45930</v>
       </c>
       <c r="B223" t="n">
-        <v>234.4277191162109</v>
+        <v>234.4277038574219</v>
       </c>
       <c r="C223" t="n">
         <v>239.3800048828125</v>
@@ -6454,7 +6454,7 @@
         <v>45961</v>
       </c>
       <c r="B224" t="n">
-        <v>205.7044830322266</v>
+        <v>205.7044677734375</v>
       </c>
       <c r="C224" t="n">
         <v>210.0500030517578</v>
